--- a/PTBR-COM-PORTRAIT/Lang/PTBR/Dialog/Drama/tyche.xlsx
+++ b/PTBR-COM-PORTRAIT/Lang/PTBR/Dialog/Drama/tyche.xlsx
@@ -515,7 +515,7 @@
           <t>Hunting androids is a blast!</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L8" s="17" t="inlineStr">
         <is>
           <t>Caçar androides é demais!</t>
         </is>
@@ -555,9 +555,9 @@
           <t>Do you have any work?</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Você tem algum trabalho?</t>
+      <c r="L9" s="17" t="inlineStr">
+        <is>
+          <t>Tem algum trabalho?</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
           <t>The work is done.</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="L10" s="17" t="inlineStr">
         <is>
           <t>O trabalho está feito.</t>
         </is>
@@ -650,10 +650,10 @@
 I have an amazing job for you. You might just become humanity’s savior!☆</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>Ei você!
-Tenho um trabalho incrível para você. Você pode se tornar o salvador da humanidade! ☆</t>
+      <c r="L16" s="17" t="inlineStr">
+        <is>
+          <t>Ei, você!
+Tenho um trabalho incrível para você. Você pode se tornar o salvador da humanidade!☆</t>
         </is>
       </c>
     </row>
@@ -681,9 +681,9 @@
           <t>I accept. (Danger Level: 38)</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>Eu aceito. (Nível de Perigo: 38)</t>
+      <c r="L17" s="17" t="inlineStr">
+        <is>
+          <t>Aceito. (Nível de Perigo: 38)</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
           <t>Maybe another time.</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="L18" s="17" t="inlineStr">
         <is>
           <t>Talvez outra hora.</t>
         </is>
@@ -773,10 +773,10 @@
 And this is my partner, VISHNU.</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>Escolha inteligente ♡ - Você não vai se arrepender!
-Ah, é mesmo, ainda não me apresentei. Me chame de Tyche ☆
+      <c r="L26" s="17" t="inlineStr">
+        <is>
+          <t>Escolha esperta♡ Não vai se arrepender!
+Ah, verdade, ainda não me apresentei. Pode me chamar de Tyche☆
 E este é meu parceiro, VISHNU.</t>
         </is>
       </c>
@@ -800,9 +800,9 @@
           <t>...NICE TO MEET YOU.</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>...PRAZER EM CONHECÊ-LO.</t>
+      <c r="L27" s="17" t="inlineStr">
+        <is>
+          <t>...MUITO PRAZER.</t>
         </is>
       </c>
     </row>
@@ -828,11 +828,11 @@
 And the flavor of this “Dragons &amp; Spices” curry completely blew me away!</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>Então, escute com atenção. Você já comeu curry antes?
-É tão delicioso e viciante que depois que você experimenta, não consegue mais viver sem. Estamos viajando pelo mundo em busca de diferentes tipos de curry.
-E o sabor deste curry "Dragons &amp; Spices" me impressionou completamente!</t>
+      <c r="L29" s="17" t="inlineStr">
+        <is>
+          <t>Então, escute com atenção. Você já comeu curry alguma vez?
+É tão delicioso e viciante que depois da primeira vez não tem volta. Andamos pelo mundo em busca de tipos diferentes de curry.
+E o sabor deste curry "Dragões e Especiarias" me explodiu a cabeça!</t>
         </is>
       </c>
     </row>
@@ -854,11 +854,11 @@
 Of course, you can’t just not investigate it, can you?♡</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>A carne, os legumes, as especiarias, tudo estava de outro mundo! Isso não é normal... você também sente isso, não é?
-Se pudéssemos descobrir o segredo por trás daquele sabor, a cultura humana poderia evoluir para o próximo estágio... ou talvez não, mas ainda assim — você entende o que quero dizer, certo?
-Claro, você não pode simplesmente não investigar isso, pode? ♡</t>
+      <c r="L30" s="17" t="inlineStr">
+        <is>
+          <t>A carne, os legumes, as especiarias, tudo era fora deste mundo! Isto não é normal... você sente também, certo?
+Se descobrirmos o segredo por trás daquele sabor, a cultura humana pode evoluir para o próximo estágio... ou talvez não, mas enfim: você me entende, certo?
+E claro que não dá para simplesmente não investigar, né?♡</t>
         </is>
       </c>
     </row>
@@ -880,11 +880,11 @@
 It doesn’t look too dangerous, but a junk android and a delicate little girl can’t exactly handle it alone... so you’ll help us, won’t you? You’ll cooperate, right? Right?♡</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>Em primeiro lugar, por que abrir um restaurante em um lugar tão remoto?
-E aquela ruína por perto. Você não sente um cheiro estranho? Pode haver algum ingrediente lendário escondido no subsolo!
-Não parece muito perigoso, mas um androide de sucata e uma garotinha delicada não conseguem lidar com isso sozinhos... então você vai nos ajudar, não vai? Você vai cooperar, certo? Certo? ♡</t>
+      <c r="L31" s="17" t="inlineStr">
+        <is>
+          <t>Antes de tudo, por que abrir um restaurante num lugar tão remoto?
+E aquela ruína perto daí. Não sente um cheiro estranho? Pode haver um ingrediente lendário escondido no subsolo!
+Não parece perigoso demais, mas um androide sucata e uma garotinha delicada não dão conta sozinhas... então você vai nos ajudar, né? Vai cooperar, né? Né?♡</t>
         </is>
       </c>
     </row>
@@ -904,10 +904,10 @@
 Then we’ll wait here while you explore the underground ruins☆ </t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>Ahh, estou tão feliz que você é um aventureiro tão esperto ♡
-Então vamos esperar aqui enquanto você explora as ruínas subterrâneas☆</t>
+      <c r="L32" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ahh, que bom que você é um aventureiro esperto♡
+Então ficaremos aqui enquanto você explora as ruínas subterrâneas☆ </t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
           <t>...GOOD LUCK.</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="L33" s="17" t="inlineStr">
         <is>
           <t>...BOA SORTE.</t>
         </is>
@@ -964,7 +964,7 @@
           <t>Oh? Really?</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="L37" s="17" t="inlineStr">
         <is>
           <t>Oh? Sério?</t>
         </is>
@@ -1000,10 +1000,10 @@
 I thought I felt the ground shake earlier, but—wait, what!? There was an underground factory run by machines, and a giant robot attacked you!?</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>Você voltou inteiro☆
-Achei que tinha sentido o chão tremer mais cedo, mas—espera, o quê!? Havia uma fábrica subterrânea comandada por máquinas, e um robô gigante te atacou!?</t>
+      <c r="L42" s="17" t="inlineStr">
+        <is>
+          <t>Voltou inteirinho☆
+Achei que senti o chão tremer há pouco, mas: espera, o quê!? Havia uma fábrica subterrânea comandada por máquinas, e um robô gigante te atacou!?</t>
         </is>
       </c>
     </row>
@@ -1025,11 +1025,11 @@
 And the curry chef must’ve used ingredients from those ruins to create his mind-blowing curry.</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>Agora entendo.
-Deve ter sido uma fazenda subterrânea de Eyth Terre. Mesmo depois que os humanos desapareceram, as máquinas continuaram produzindo comida sem parar.
-E o chef de curry deve ter usado ingredientes dessas ruínas para criar seu curry alucinante.</t>
+      <c r="L43" s="17" t="inlineStr">
+        <is>
+          <t>Entendi agora.
+Devia ser uma fazenda subterrânea de Eyth Terre. Mesmo depois de os humanos sumirem, as máquinas seguiram produzindo comida sem parar.
+E o chef do curry deve ter usado ingredientes dessas ruínas para criar o curry absurdo dele.</t>
         </is>
       </c>
     </row>
@@ -1052,9 +1052,9 @@
           <t>...IT'S ALL GONE NOW. A TRAGEDY.</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>...ESTÁ TUDO ACABADO AGORA. UMA TRAGÉDIA.</t>
+      <c r="L44" s="17" t="inlineStr">
+        <is>
+          <t>...ACABOU TUDO AGORA. UMA TRAGÉDIA.</t>
         </is>
       </c>
     </row>
@@ -1074,10 +1074,10 @@
 Listen #pc, if you’re an adventurer, remember this: not every adventure ends in a happy ending.</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>B-bem, tudo bem! Um cara forte como aquele chef vai encontrar um jeito de continuar mesmo sem a fazenda subterrânea☆
-Escute #pc, se você é um aventureiro, lembre-se disso: nem toda aventura termina com um final feliz.</t>
+      <c r="L45" s="17" t="inlineStr">
+        <is>
+          <t>B-bom, tá tudo bem! Um garotão forte como aquele chef vai achar um jeito de seguir em frente até sem a fazenda subterrânea☆
+Escuta #pc, se você é aventureiro, grave isto: nem toda aventura termina em final feliz.</t>
         </is>
       </c>
     </row>
@@ -1113,12 +1113,12 @@
 Oh, and if you ever run out of the seed, the chef here might sell you more.</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>Aqui, pegue esta semente especial. Anime-se♡
-Pense desta forma. Aquelas pobres máquinas, ainda se movendo muito tempo depois de perderem seu propósito... nós finalmente demos a elas um descanso pacífico!
-De qualquer forma, vamos sair de fininho antes que alguém perceba☆
-Ah, e se você ficar sem a semente, o chef aqui pode vender mais para você.</t>
+      <c r="L47" s="17" t="inlineStr">
+        <is>
+          <t>Toma, leve esta semente especial. Anima♡
+Pense assim: aquelas máquinas pobres, ainda se mexendo muito depois de perder o propósito... finalmente demos a elas um descanso em paz!
+Enfim, vamos dar o fora antes que alguém perceba☆
+Ah, e se acabar a semente, o chef daqui pode te vender mais.</t>
         </is>
       </c>
     </row>
@@ -1141,9 +1141,9 @@
           <t>...GOOD BYE.</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>...ADEUS.</t>
+      <c r="L48" s="17" t="inlineStr">
+        <is>
+          <t>...ATÉ LOGO.</t>
         </is>
       </c>
     </row>
